--- a/eval-suite/cases/T3_missing_data_source_clean/mapping.xlsx
+++ b/eval-suite/cases/T3_missing_data_source_clean/mapping.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
